--- a/bom/bom-prototype.xlsx
+++ b/bom/bom-prototype.xlsx
@@ -450,14 +450,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="56" customWidth="1" min="1" max="1"/>
     <col width="43" customWidth="1" min="2" max="2"/>
     <col width="5" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="56" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,7 +472,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Off-the-shelf build on the Seeed XIAO nRF52840 Sense. Prices are approximate street prices.</t>
+          <t>Off-the-shelf build on the Seeed XIAO nRF52840 Sense. Everything ordered from Amazon; prices are approximate.</t>
         </is>
       </c>
     </row>
@@ -498,6 +500,16 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Amazon search term</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
@@ -524,11 +536,21 @@
         <v>1</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>$15.99 direct from Seeed (ships from China); Amazon if needed this week</t>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Seeed Studio XIAO nRF52840 Sense</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>A few dollars over Seeed direct, but arrives in days, not weeks</t>
         </is>
       </c>
     </row>
@@ -549,7 +571,17 @@
       <c r="D7" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>ballpoint pen thick barrel</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -568,7 +600,21 @@
       <c r="D8" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="E8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>USB-C data cable</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Charge-only cables will not enumerate; check the listing says data</t>
+        </is>
+      </c>
     </row>
     <row r="9"/>
     <row r="10">
@@ -586,18 +632,28 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>3.7 V 300 mAh, JST-PH, protected</t>
+          <t>3.7 V 300 mAh, JST-PH 2.0, protected</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>XIAO has the charger onboard; plugs straight in</t>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>3.7V 300mAh LiPo JST-PH 2.0 protection</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>XIAO has the charger onboard; plugs straight in. Check connector polarity against the XIAO silkscreen before plugging</t>
         </is>
       </c>
     </row>
@@ -616,9 +672,23 @@
         <v>1</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="5" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>SPDT slide switch small</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Sold in multipacks</t>
+        </is>
+      </c>
     </row>
     <row r="13"/>
     <row r="14">
@@ -643,11 +713,21 @@
         <v>1</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Super-glued to the back of the XIAO</t>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>mini hose clamp 8-12mm</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Sold in multipacks; super-glued to the back of the XIAO</t>
         </is>
       </c>
     </row>
@@ -670,9 +750,15 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Nothing conductive may touch the exposed pads on the board back</t>
-        </is>
-      </c>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>super glue gel</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr"/>
     </row>
     <row r="17"/>
     <row r="18">
@@ -682,7 +768,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19"/>
@@ -696,12 +782,19 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Leave the BAT pads uncovered if the cell might be added later.</t>
+          <t>Nothing conductive may touch the exposed pads on the back of the board.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Leave the BAT pads uncovered if the cell might be added later.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Laptop software (Pure Data, bridge, dashboard) is free and not part of this BOM.</t>
         </is>

--- a/bom/bom-prototype.xlsx
+++ b/bom/bom-prototype.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -692,109 +692,39 @@
     </row>
     <row r="13"/>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Mount</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Hose clamp</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Small worm-drive, sized to the pen barrel</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>mini hose clamp 8-12mm</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>Sold in multipacks; super-glued to the back of the XIAO</t>
-        </is>
-      </c>
-    </row>
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Total, everything</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Super glue</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>Cyanoacrylate</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>super glue gel</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr"/>
-    </row>
-    <row r="17"/>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Keep metal away from the USB-C end of the XIAO: the BLE antenna lives there.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Nothing conductive may touch the exposed pads on the back of the board.</t>
+        </is>
+      </c>
+    </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Total, everything</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Keep metal away from the USB-C end of the XIAO: the BLE antenna lives there.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Nothing conductive may touch the exposed pads on the back of the board.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Leave the BAT pads uncovered if the cell might be added later.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Laptop software (Pure Data, bridge, dashboard) is free and not part of this BOM.</t>
         </is>

--- a/bom/bom-prototype.xlsx
+++ b/bom/bom-prototype.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,26 +26,48 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Red Hat Display"/>
       <b val="1"/>
-      <sz val="14"/>
+      <color rgb="00151515"/>
+      <sz val="15"/>
     </font>
     <font>
+      <name val="Red Hat Text"/>
       <i val="1"/>
-      <color rgb="007F7F7F"/>
+      <color rgb="006A6E73"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="Red Hat Text"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="Red Hat Display"/>
       <b val="1"/>
-      <sz val="12"/>
+      <color rgb="00151515"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="Red Hat Text"/>
+      <color rgb="00151515"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Red Hat Display"/>
       <b val="1"/>
+      <color rgb="000066CC"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Red Hat Text"/>
+      <i val="1"/>
+      <color rgb="006A6E73"/>
+      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -54,7 +76,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E5F"/>
+        <fgColor rgb="00151515"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F5F5"/>
       </patternFill>
     </fill>
   </fills>
@@ -68,14 +95,14 @@
     </border>
     <border>
       <bottom style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00D2D2D2"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -83,8 +110,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -453,13 +484,13 @@
   <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="56" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
     <col width="5" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="56" customWidth="1" min="7" max="7"/>
+    <col width="54" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,12 +503,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Off-the-shelf build on the Seeed XIAO nRF52840 Sense. Everything ordered from Amazon; prices are approximate.</t>
+          <t>Off-the-shelf build on the Seeed XIAO nRF52840 Sense. Everything ordered from Amazon; prices approximate.</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4">
+    <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Item</t>
@@ -535,7 +566,7 @@
       <c r="C6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="6" t="n">
         <v>20</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -550,38 +581,38 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>A few dollars over Seeed direct, but arrives in days, not weeks</t>
+          <t>A few dollars over Seeed direct, but arrives in days</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Pen</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Any ballpoint, thicker barrel</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>ballpoint pen thick barrel</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr"/>
+      <c r="G7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -597,7 +628,7 @@
       <c r="C8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="6" t="n">
         <v>8</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -612,7 +643,7 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Charge-only cables will not enumerate; check the listing says data</t>
+          <t>Charge-only cables will not enumerate</t>
         </is>
       </c>
     </row>
@@ -625,35 +656,35 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>LiPo cell</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>3.7 V 300 mAh, JST-PH 2.0, protected</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>3.7V 300mAh LiPo JST-PH 2.0 protection</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>XIAO has the charger onboard; plugs straight in. Check connector polarity against the XIAO silkscreen before plugging</t>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Check polarity against the XIAO silkscreen before plugging</t>
         </is>
       </c>
     </row>
@@ -671,7 +702,7 @@
       <c r="C12" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="5" t="n">
+      <c r="D12" s="6" t="n">
         <v>6</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -692,39 +723,39 @@
     </row>
     <row r="13"/>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Total, everything</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="9" t="n">
         <v>46</v>
       </c>
     </row>
     <row r="15"/>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>Keep metal away from the USB-C end of the XIAO: the BLE antenna lives there.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>Nothing conductive may touch the exposed pads on the back of the board.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>Leave the BAT pads uncovered if the cell might be added later.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>Laptop software (Pure Data, bridge, dashboard) is free and not part of this BOM.</t>
         </is>

--- a/bom/bom-prototype.xlsx
+++ b/bom/bom-prototype.xlsx
@@ -507,7 +507,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -586,33 +585,33 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Pen</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Any ballpoint, thicker barrel</t>
         </is>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>ballpoint pen thick barrel</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -656,33 +655,33 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>LiPo cell</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>3.7 V 300 mAh, JST-PH 2.0, protected</t>
         </is>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="D11" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>3.7V 300mAh LiPo JST-PH 2.0 protection</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Check polarity against the XIAO silkscreen before plugging</t>
         </is>
